--- a/data/out/variants/v9_date_range_all/summary_v9_date_range_all.xlsx
+++ b/data/out/variants/v9_date_range_all/summary_v9_date_range_all.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-2.166279284717999</v>
+        <v>-2.166279284718812</v>
       </c>
       <c r="F2" t="n">
-        <v>143.3518414533981</v>
+        <v>143.3518414534191</v>
       </c>
       <c r="G2" t="n">
-        <v>30665.87576398336</v>
+        <v>30665.87576399124</v>
       </c>
       <c r="H2" t="n">
-        <v>175.1167489533293</v>
+        <v>175.1167489533518</v>
       </c>
       <c r="I2" t="n">
-        <v>110.8194027648357</v>
+        <v>110.8194027648596</v>
       </c>
       <c r="J2" t="n">
         <v>13105</v>
@@ -547,7 +547,7 @@
         <v>2621</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02045035362243652</v>
+        <v>0.04568648338317871</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-2.140774364195816</v>
+        <v>-2.140870188027689</v>
       </c>
       <c r="F3" t="n">
-        <v>142.691918755683</v>
+        <v>142.6942304523117</v>
       </c>
       <c r="G3" t="n">
-        <v>30418.85689616634</v>
+        <v>30419.78496392639</v>
       </c>
       <c r="H3" t="n">
-        <v>174.4100252169191</v>
+        <v>174.4126857884093</v>
       </c>
       <c r="I3" t="n">
-        <v>110.2712393089002</v>
+        <v>110.2735276343429</v>
       </c>
       <c r="J3" t="n">
         <v>13105</v>
@@ -598,7 +598,7 @@
         <v>2621</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01824522018432617</v>
+        <v>0.03615713119506836</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-1.792282805115289</v>
+        <v>-1.798692528818969</v>
       </c>
       <c r="F4" t="n">
-        <v>132.9678009861978</v>
+        <v>133.140143588383</v>
       </c>
       <c r="G4" t="n">
-        <v>27043.66541917315</v>
+        <v>27105.74452625861</v>
       </c>
       <c r="H4" t="n">
-        <v>164.4495832137411</v>
+        <v>164.638223162966</v>
       </c>
       <c r="I4" t="n">
-        <v>103.5597246749418</v>
+        <v>103.7262825360503</v>
       </c>
       <c r="J4" t="n">
         <v>13105</v>
@@ -649,7 +649,7 @@
         <v>2621</v>
       </c>
       <c r="M4" t="n">
-        <v>2.312837362289429</v>
+        <v>4.177455425262451</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-11.80172111034987</v>
+        <v>-11.78946407460598</v>
       </c>
       <c r="F5" t="n">
-        <v>337.7900755827624</v>
+        <v>337.6437391133029</v>
       </c>
       <c r="G5" t="n">
-        <v>123986.5324041106</v>
+        <v>123867.8212287664</v>
       </c>
       <c r="H5" t="n">
-        <v>352.1172140127639</v>
+        <v>351.9486059480367</v>
       </c>
       <c r="I5" t="n">
-        <v>286.0529211945394</v>
+        <v>285.8834992291904</v>
       </c>
       <c r="J5" t="n">
         <v>13105</v>
@@ -704,7 +704,7 @@
         <v>2621</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9498341083526611</v>
+        <v>5.21685266494751</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-497.6676052476535</v>
+        <v>-497.5105955585014</v>
       </c>
     </row>
     <row r="6">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-0.8594765416793886</v>
+        <v>-0.8594765416793884</v>
       </c>
       <c r="F6" t="n">
         <v>100.6316982955585</v>
@@ -749,7 +749,7 @@
         <v>134.1987368651291</v>
       </c>
       <c r="I6" t="n">
-        <v>80.80078396323029</v>
+        <v>80.80078396323027</v>
       </c>
       <c r="J6" t="n">
         <v>13105</v>
@@ -761,7 +761,7 @@
         <v>2621</v>
       </c>
       <c r="M6" t="n">
-        <v>2.101526498794556</v>
+        <v>10.02586770057678</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-512.2687938591329</v>
+        <v>-515.0893990804633</v>
       </c>
     </row>
     <row r="7">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-1.271508840741431</v>
+        <v>-1.283832560155147</v>
       </c>
       <c r="F7" t="n">
-        <v>127.2871370453234</v>
+        <v>127.680799094808</v>
       </c>
       <c r="G7" t="n">
-        <v>21999.89376905853</v>
+        <v>22119.25078545162</v>
       </c>
       <c r="H7" t="n">
-        <v>148.3236116370503</v>
+        <v>148.7254207775242</v>
       </c>
       <c r="I7" t="n">
-        <v>104.5287875673744</v>
+        <v>104.8614596627405</v>
       </c>
       <c r="J7" t="n">
         <v>13105</v>
@@ -818,7 +818,7 @@
         <v>2621</v>
       </c>
       <c r="M7" t="n">
-        <v>187.2189798355103</v>
+        <v>289.9319798946381</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-501.1835372486068</v>
+        <v>-499.7673168876093</v>
       </c>
     </row>
     <row r="8">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-6.479223123521946</v>
+        <v>-6.483304378757901</v>
       </c>
       <c r="F8" t="n">
-        <v>259.4556513084605</v>
+        <v>259.5834879705498</v>
       </c>
       <c r="G8" t="n">
-        <v>72437.36464563422</v>
+        <v>72476.89219667211</v>
       </c>
       <c r="H8" t="n">
-        <v>269.1419042914615</v>
+        <v>269.2153268234781</v>
       </c>
       <c r="I8" t="n">
-        <v>219.1420535979302</v>
+        <v>219.2599094726523</v>
       </c>
       <c r="J8" t="n">
         <v>13105</v>
@@ -875,7 +875,7 @@
         <v>2621</v>
       </c>
       <c r="M8" t="n">
-        <v>189.8822293281555</v>
+        <v>159.1125926971436</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-454.9015422315231</v>
+        <v>-453.4272282066672</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-18.45731005374891</v>
+        <v>-18.45820974483968</v>
       </c>
       <c r="F9" t="n">
-        <v>427.6706484726797</v>
+        <v>427.6808912432999</v>
       </c>
       <c r="G9" t="n">
-        <v>188446.8801250142</v>
+        <v>188455.5937641896</v>
       </c>
       <c r="H9" t="n">
-        <v>434.104687978619</v>
+        <v>434.1147241964843</v>
       </c>
       <c r="I9" t="n">
-        <v>357.780690460608</v>
+        <v>357.7889361125024</v>
       </c>
       <c r="J9" t="n">
         <v>13105</v>
@@ -932,7 +932,7 @@
         <v>2621</v>
       </c>
       <c r="M9" t="n">
-        <v>29.92409753799438</v>
+        <v>21.64433097839355</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-482.7828147915604</v>
+        <v>-482.7836103252114</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-2.278576488520217</v>
+        <v>-2.357834854625155</v>
       </c>
       <c r="F10" t="n">
-        <v>141.3936245707745</v>
+        <v>143.7286537308552</v>
       </c>
       <c r="G10" t="n">
-        <v>31753.4905290682</v>
+        <v>32521.11934183946</v>
       </c>
       <c r="H10" t="n">
-        <v>178.1950912036249</v>
+        <v>180.3361287757932</v>
       </c>
       <c r="I10" t="n">
-        <v>117.8788853033957</v>
+        <v>119.5983990115151</v>
       </c>
       <c r="J10" t="n">
         <v>13105</v>
@@ -989,7 +989,7 @@
         <v>2621</v>
       </c>
       <c r="M10" t="n">
-        <v>0.777268648147583</v>
+        <v>0.6960430145263672</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-572.6871695083522</v>
+        <v>-570.4216195827229</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 753, 'learning_rate': 0.06273187009500597, 'max_depth': 9, 'subsample': 0.9540684534887596, 'colsample_bytree': 0.7861877126350728}</t>
+          <t>{'n_estimators': 218, 'learning_rate': 0.010702752670026279, 'max_depth': 9, 'subsample': 0.6780503218493269, 'colsample_bytree': 0.7611870670189212}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-2.897479961343939</v>
+        <v>-3.987168406569881</v>
       </c>
       <c r="F11" t="n">
-        <v>161.69827391635</v>
+        <v>197.1097178813494</v>
       </c>
       <c r="G11" t="n">
-        <v>37747.66075249512</v>
+        <v>48301.45196226931</v>
       </c>
       <c r="H11" t="n">
-        <v>194.2875723058351</v>
+        <v>219.7759130620763</v>
       </c>
       <c r="I11" t="n">
-        <v>134.8551245814507</v>
+        <v>166.2653573489897</v>
       </c>
       <c r="J11" t="n">
         <v>13105</v>
@@ -1046,7 +1046,7 @@
         <v>2621</v>
       </c>
       <c r="M11" t="n">
-        <v>204.3232817649841</v>
+        <v>112.8434727191925</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 454, 'learning_rate': 0.03866875514143172, 'num_leaves': 31, 'min_child_samples': 13}</t>
+          <t>{'n_estimators': 200, 'learning_rate': 0.01230485414404867, 'num_leaves': 94, 'min_child_samples': 42}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-2.37569900153126</v>
+        <v>-2.269539340621172</v>
       </c>
       <c r="F12" t="n">
-        <v>153.0106201015636</v>
+        <v>153.4125331627204</v>
       </c>
       <c r="G12" t="n">
-        <v>32694.13620497475</v>
+        <v>31665.96443619622</v>
       </c>
       <c r="H12" t="n">
-        <v>180.8151990430416</v>
+        <v>177.9493310922978</v>
       </c>
       <c r="I12" t="n">
-        <v>128.4040652820408</v>
+        <v>128.5497500525113</v>
       </c>
       <c r="J12" t="n">
         <v>13105</v>
@@ -1101,7 +1101,7 @@
         <v>2621</v>
       </c>
       <c r="M12" t="n">
-        <v>263.3493554592133</v>
+        <v>300.8762187957764</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 239, 'learning_rate': 0.02942850633247973, 'depth': 8}</t>
+          <t>{'iterations': 329, 'learning_rate': 0.012147425502786689, 'depth': 8}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-3.716057285012635</v>
+        <v>-3.6207567213266</v>
       </c>
       <c r="F13" t="n">
-        <v>188.6612576531903</v>
+        <v>191.8644470235048</v>
       </c>
       <c r="G13" t="n">
-        <v>45675.70128637808</v>
+        <v>44752.7014548917</v>
       </c>
       <c r="H13" t="n">
-        <v>213.7187434138103</v>
+        <v>211.5483430681784</v>
       </c>
       <c r="I13" t="n">
-        <v>158.8883853890516</v>
+        <v>161.5682171570706</v>
       </c>
       <c r="J13" t="n">
         <v>13105</v>
@@ -1156,7 +1156,7 @@
         <v>2621</v>
       </c>
       <c r="M13" t="n">
-        <v>313.4293210506439</v>
+        <v>245.0066041946411</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-1.722934316912575</v>
+        <v>-1.42209188767071</v>
       </c>
       <c r="F14" t="n">
-        <v>136.1198493323159</v>
+        <v>130.2528461049579</v>
       </c>
       <c r="G14" t="n">
-        <v>26372.0152163914</v>
+        <v>23458.31249781152</v>
       </c>
       <c r="H14" t="n">
-        <v>162.3946280404355</v>
+        <v>153.1610671737812</v>
       </c>
       <c r="I14" t="n">
-        <v>113.9559227074543</v>
+        <v>108.7881426587478</v>
       </c>
       <c r="J14" t="n">
         <v>13105</v>
@@ -1211,7 +1211,7 @@
         <v>2621</v>
       </c>
       <c r="M14" t="n">
-        <v>71.91780471801758</v>
+        <v>62.42213439941406</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-554.7467445224994</v>
+        <v>-556.6839598732022</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>2621</v>
       </c>
       <c r="M15" t="n">
-        <v>23.04858326911926</v>
+        <v>20.76386523246765</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-2.488811390492431</v>
+        <v>-2.43989419892071</v>
       </c>
       <c r="F16" t="n">
-        <v>152.112587187886</v>
+        <v>151.3809003190261</v>
       </c>
       <c r="G16" t="n">
-        <v>33789.64615698443</v>
+        <v>33315.87603610422</v>
       </c>
       <c r="H16" t="n">
-        <v>183.8196022109297</v>
+        <v>182.5263707963981</v>
       </c>
       <c r="I16" t="n">
-        <v>121.1077046074472</v>
+        <v>122.0524804206474</v>
       </c>
       <c r="J16" t="n">
         <v>13105</v>
@@ -1325,7 +1325,7 @@
         <v>2621</v>
       </c>
       <c r="M16" t="n">
-        <v>524.9395039081573</v>
+        <v>487.9385550022125</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-513.6266176118311</v>
+        <v>-513.1319062704807</v>
       </c>
     </row>
   </sheetData>
